--- a/backtest_runs/20260410_193658/by_symbol/AKGL/AKGL.xlsx
+++ b/backtest_runs/20260410_193658/by_symbol/AKGL/AKGL.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0</v>
